--- a/onagawa/output/女川町_上下水道_中間報告用_修正前後の指標分析と数値修正.xlsx
+++ b/onagawa/output/女川町_上下水道_中間報告用_修正前後の指標分析と数値修正.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_基幹ファイル修正指示" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_改定案の再計算" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_住民議会説明用_差替案" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_前提と限界" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -144,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -191,6 +192,9 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -205,9 +209,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -251,14 +252,20 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -812,7 +819,7 @@
         <is>
           <t>掲載22.07％
 明細書からの算定 5,319,896,544／14,403,468,966＝36.93％
-（修正前累計額＋当年度償却で算定すると22.02％となり掲載値にほぼ一致）</t>
+分子・分母の８通りを検証した結果、修正前の累計額を分子とする場合のみ21.9〜22.2％となり掲載値を含む</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
@@ -845,104 +852,136 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>■　本ファイルを読む前に　※シート08「前提と限界」を必ずご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>本ファイルには、決算書・意見書の記載どおりの【確定値】と、当方が推計・推定した値が混在しています。シート08で区別を明示しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>特に次の３点は推計・推定です。　① 令和６年度末の流動資産・流動負債（千円単位の推計）　② 累積欠損金比率の分母となる令和６年度の営業収益（概算）　③ 決算書掲載値22.07％の算定根拠（外部からの推定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>また、令和６年度の「修正後」の数値は、過年度修正を遡及反映した場合の試算値（プロフォーマ）であり、公表された決算値ではありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>■　用いた資料</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>資　料</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>使用箇所</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>備　考</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>令和７年度 女川町上水道事業会計決算書</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>貸借対照表・剰余金計算書・有形固定資産明細書・財務分析表・経営指標の推移</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>剰余金計算書の「前年度末残高」が令和６年度末の修正前の値</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>令和７年度 水道分決算審査意見書（案）</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>「参考　過年度審査指摘事項」の修正前・修正後の額</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>上水道４件・下水道２件。いずれも令和６年度決算における額</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>女川町_水道 経営戦略試算シート20251209版.xlsx</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>「有収水量別」シート（調定データ１か月分）</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>★個人が特定されうるため、本ファイルには水量帯別・口径別の集計のみを掲載</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>onagawa_rate_reform_v1.xlsx</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>修正対象の基幹ファイル</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>８シート構成</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1029,13 +1068,13 @@
           <t>剰余金　資本剰余金（補助金）</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>5812974385</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>239689468</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>-5573284917</v>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
@@ -1051,13 +1090,13 @@
           <t>繰延収益　長期前受金</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>5477657479</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <v>11050942396</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>5573284917</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
@@ -1073,13 +1112,13 @@
           <t>流動資産　その他流動資産</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>169933187</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>-169933187</v>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
@@ -1095,13 +1134,13 @@
           <t>建物減価償却累計額</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="19" t="n">
         <v>-121601517</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="19" t="n">
         <v>-131734934</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <v>-10133417</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
@@ -1117,13 +1156,13 @@
           <t>構築物減価償却累計額</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>-1564522418</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>-3031943076</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>-1467420658</v>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
@@ -1139,13 +1178,13 @@
           <t>機械及び装置減価償却累計額</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>-1080753034</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="19" t="n">
         <v>-1759309677</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <v>-678556643</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
@@ -1161,13 +1200,13 @@
           <t>繰延収益　長期前受金収益化累計額</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>-2467811261</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>-3234327941</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>-766516680</v>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -1183,13 +1222,13 @@
           <t>固定資産　量水器</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>14171669</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>10543340</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>-3628329</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
@@ -1205,13 +1244,13 @@
           <t>固定資産　量水器減価償却累計額</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>-10635904</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>-2285255</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>8350649</v>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
@@ -1227,13 +1266,13 @@
           <t>建設仮勘定</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>177558</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>-177558</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
@@ -1249,19 +1288,19 @@
           <t>流動資産　貯蔵品</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>5303463</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>1680250</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <v>-3623213</v>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>★合計（純額）</t>
         </is>
@@ -1271,9 +1310,9 @@
           <t>資産△／繰延収益＋／資本剰余金△</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr"/>
-      <c r="D17" s="20" t="inlineStr"/>
-      <c r="E17" s="20" t="inlineStr"/>
+      <c r="C17" s="21" t="inlineStr"/>
+      <c r="D17" s="21" t="inlineStr"/>
+      <c r="E17" s="21" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr">
         <is>
           <t>下段【修正の純影響額】を参照</t>
@@ -1281,28 +1320,28 @@
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>① 平成23年度の会計基準見直し（平成26年度決算から適用）が未対応で、資本剰余金5,573,284,917円を繰延収益の長期前受金に振り替える必要があった。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>② 平成29〜令和２年度の消費税申告に係る仮払消費税の取崩し処理で、還付金を未収金で消込漏れとなり不用額となっていた。全額を特別損失として処理。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>③ 決算書の固定資産明細書と貸借対照表の計数不一致。令和３年度の特別損益の未処理が原因。特別利益・特別損失を計上のうえ処理。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>④ 量水器の除却等の台帳未修正、現地未撤去、減価償却方法の誤りによる錯誤。特別損失を計上のうえ処理。</t>
         </is>
@@ -1358,13 +1397,13 @@
           <t>無形固定資産　施設利用権</t>
         </is>
       </c>
-      <c r="C26" s="17" t="n">
+      <c r="C26" s="18" t="n">
         <v>1187111818</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <v>1018241974</v>
       </c>
-      <c r="E26" s="17" t="n">
+      <c r="E26" s="18" t="n">
         <v>-168869844</v>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
@@ -1380,13 +1419,13 @@
           <t>固定資産　構築物減価償却累計額</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="19" t="n">
         <v>-642507537</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="19" t="n">
         <v>-643047483</v>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="19" t="n">
         <v>-539946</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
@@ -1402,33 +1441,33 @@
           <t>長期前受金収益化累計額</t>
         </is>
       </c>
-      <c r="C28" s="17" t="n">
+      <c r="C28" s="18" t="n">
         <v>-542089066</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="18" t="n">
         <v>-542359039</v>
       </c>
-      <c r="E28" s="17" t="n">
+      <c r="E28" s="18" t="n">
         <v>-269973</v>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>① 流域下水道事業への建設費負担金に係る施設利用権について、令和４〜５年度に減価償却がされていなかった。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>② 令和３年度に計上されるべき減価償却額と長期前受金に誤りがあった。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>下水道事業の修正の純影響額は 169,139,817円（欠損金の増加）＝資産の減少169,409,790円 － 繰延収益の減少269,973円。上水道と同様に令和７年度に特別損益として処理されている。</t>
         </is>
@@ -1517,7 +1556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1575,10 +1614,10 @@
           <t>有形固定資産（償却未済高）</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>11569450875</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>9417884919</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1593,10 +1632,10 @@
           <t>無形固定資産</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <v>1889200</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>1889200</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -1611,10 +1650,10 @@
           <t>固定資産合計</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>11571340075</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>9419774119</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1629,10 +1668,10 @@
           <t>流動資産合計</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="19" t="n">
         <v>417612331</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="19" t="n">
         <v>244055931</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1665,10 +1704,10 @@
           <t>負債合計（固定＋流動）</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="19" t="n">
         <v>1190291617</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>1190291617</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -1683,10 +1722,10 @@
           <t>繰延収益（長期前受金＋収益化累計額）</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <v>3009846218</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>7816614455</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1701,10 +1740,10 @@
           <t>資本金</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>1384031753</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>1384031753</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -1719,10 +1758,10 @@
           <t>資本剰余金</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="18" t="n">
         <v>7559417559</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>1986132642</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1755,10 +1794,10 @@
           <t>資本合計</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="18" t="n">
         <v>7788814571</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>656923978</v>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1773,10 +1812,10 @@
           <t>自己資本（資本合計＋繰延収益）</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="19" t="n">
         <v>10798660789</v>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>8473538433</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -1820,7 +1859,7 @@
           <t>資産の減少</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n">
+      <c r="B21" s="18" t="n">
         <v>-2325122356</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1840,7 +1879,7 @@
           <t>繰延収益の増加</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="19" t="n">
         <v>4806768237</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -1860,7 +1899,7 @@
           <t>資本剰余金の減少</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="18" t="n">
         <v>-5573284917</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1929,7 +1968,7 @@
           <t>特別利益（令和７年度）</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n">
+      <c r="B28" s="18" t="n">
         <v>774867329</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1949,7 +1988,7 @@
           <t>特別損失（令和７年度）</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="19" t="n">
         <v>-2333576494</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -1969,7 +2008,7 @@
           <t>特別損益 純額</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="18" t="n">
         <v>-1558709165</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1989,7 +2028,7 @@
           <t>うち当年度分（水道料金不納欠損等）</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="19" t="n">
         <v>-103489</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -2053,7 +2092,7 @@
           <t>令和６年度末 未処理欠損金（修正後）</t>
         </is>
       </c>
-      <c r="B36" s="17" t="n">
+      <c r="B36" s="18" t="n">
         <v>-2713240417</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2068,7 +2107,7 @@
           <t>令和７年度 実質純損失</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="19" t="n">
         <v>-19693133</v>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -2093,26 +2132,110 @@
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>この検証により、決算審査意見書に記載された修正前・修正後の額と、令和７年度決算に計上された特別損益が完全に整合していることが確認できました。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>住民・議会への説明では、「過年度の会計処理誤りの修正額は15億5,861万円であり、第三者による検証で決算書との整合を確認した」と述べることができます。</t>
         </is>
       </c>
     </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>■　下水道事業の欠損金（同じ方法による検証）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>項　目</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>修正前（円）</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>修正後（円）</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>説　明</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>令和６年度末 未処理欠損金</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n">
+        <v>-312413050</v>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>-481552867</v>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>修正前は令和７年度剰余金計算書の前年度末残高。修正後は純影響額169,139,817円を反映（1.54倍）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>令和７年度 純損失</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="n">
+        <v>-228419897</v>
+      </c>
+      <c r="C46" s="19" t="n">
+        <v>-59280080</v>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>修正後は過年度修正分169,139,817円を除いた実質純損失59,280,080円</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>★令和７年度末 未処理欠損金</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="n">
+        <v>-540832947</v>
+      </c>
+      <c r="C47" s="24" t="n">
+        <v>-540832947</v>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>★どちらの経路でも決算書の値と一致（差異０円）。上水道と同じ構造で検証できた</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A2:D2"/>
@@ -2127,7 +2250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2148,14 +2271,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>決算審査意見書の修正前・修正後の額をもとに、令和６年度の貸借対照表を再構成して指標を算定したもの</t>
+          <t>★「修正後」は、過年度修正を令和６年度に遡及して反映した場合の試算値（プロフォーマ）です。令和６年度決算は既に認定済みであり、公表された決算値ではありません。修正は令和７年度の特別損益として処理されています</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■　修正の影響を受ける指標</t>
+          <t>■　修正の影響を受ける指標　※「修正後」はプロフォーマ（遡及反映した場合の試算値）</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2556,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>■　貸借対照表の主要項目（令和６年度末）</t>
+          <t>■　貸借対照表の主要項目（令和６年度末）　※「修正後」はプロフォーマ（遡及反映した場合の試算値）</t>
         </is>
       </c>
     </row>
@@ -2471,13 +2594,13 @@
           <t>有形固定資産（償却未済高）</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n">
+      <c r="B21" s="18" t="n">
         <v>11569450875</v>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="18" t="n">
         <v>9417884919</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <v>-2151565956</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2493,13 +2616,13 @@
           <t>流動資産</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="19" t="n">
         <v>417612331</v>
       </c>
-      <c r="C22" s="18" t="n">
+      <c r="C22" s="19" t="n">
         <v>244055931</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="19" t="n">
         <v>-173556400</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -2515,13 +2638,13 @@
           <t>資産合計</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="18" t="n">
         <v>11988952406</v>
       </c>
-      <c r="C23" s="17" t="n">
+      <c r="C23" s="18" t="n">
         <v>9663830050</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="18" t="n">
         <v>-2325122356</v>
       </c>
       <c r="E23" s="5" t="inlineStr"/>
@@ -2533,13 +2656,13 @@
           <t>長期前受金</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="19" t="n">
         <v>5477657479</v>
       </c>
-      <c r="C24" s="18" t="n">
+      <c r="C24" s="19" t="n">
         <v>11050942396</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="19" t="n">
         <v>5573284917</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -2555,13 +2678,13 @@
           <t>長期前受金収益化累計額</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n">
+      <c r="B25" s="18" t="n">
         <v>-2467811261</v>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C25" s="18" t="n">
         <v>-3234327941</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="18" t="n">
         <v>-766516680</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2577,13 +2700,13 @@
           <t>資本剰余金</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="19" t="n">
         <v>7559417559</v>
       </c>
-      <c r="C26" s="18" t="n">
+      <c r="C26" s="19" t="n">
         <v>1986132642</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="19" t="n">
         <v>-5573284917</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -2599,13 +2722,13 @@
           <t>未処理欠損金</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="18" t="n">
         <v>-1154634741</v>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C27" s="18" t="n">
         <v>-2713240417</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="18" t="n">
         <v>-1558605676</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2621,38 +2744,54 @@
           <t>資本合計</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="19" t="n">
         <v>7788814571</v>
       </c>
-      <c r="C28" s="18" t="n">
+      <c r="C28" s="19" t="n">
         <v>656923978</v>
       </c>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="19" t="n">
         <v>-7131890593</v>
       </c>
       <c r="E28" s="7" t="inlineStr"/>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>※ 流動資産の修正前の額417,612千円は、令和７年度決算の流動資産156,291千円に、決算審査意見書に記載された前年度比減少額261,321千円を戻して算定したものです。</t>
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>※ 流動資産の修正前の額417,612千円は、令和７年度決算の流動資産156,291千円に、決算審査意見書に記載された前年度比減少額261,321千円を戻して算定した★推計値です（千円単位）。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>※ 資本金・資本剰余金・未処理欠損金の修正前の額は、令和７年度剰余金計算書の「前年度末残高」によります。</t>
         </is>
       </c>
     </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>★ 流動資産・流動負債は千円単位の推計値です。円単位の精度はありません。流動比率111.52％も同じ誤差を引き継ぎます（シート08参照）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>★ 累積欠損金比率の分母（令和６年度の営業収益）は概算です。令和６年度のその他営業収益が未確認のため、値には±数ポイントの幅があります。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A30:F30"/>
@@ -2667,7 +2806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2731,10 +2870,10 @@
           <t>建物</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>826599519</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>146209486</v>
       </c>
       <c r="D6" s="31" t="n">
@@ -2748,10 +2887,10 @@
           <t>構築物</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <v>10008063854</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>3227397373</v>
       </c>
       <c r="D7" s="32" t="n">
@@ -2765,10 +2904,10 @@
           <t>機械及び装置</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>3555238033</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>1942559153</v>
       </c>
       <c r="D8" s="31" t="n">
@@ -2782,10 +2921,10 @@
           <t>工具、器具及び備品</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="19" t="n">
         <v>924000</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="19" t="n">
         <v>877800</v>
       </c>
       <c r="D9" s="32" t="n">
@@ -2799,10 +2938,10 @@
           <t>量水器</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>12643560</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>2852732</v>
       </c>
       <c r="D10" s="31" t="n">
@@ -2865,7 +3004,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="80" customHeight="1">
+    <row r="15" ht="64" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>令和６年度</t>
@@ -2886,7 +3025,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="80" customHeight="1">
+    <row r="16" ht="64" customHeight="1">
       <c r="A16" s="35" t="inlineStr">
         <is>
           <t>★令和７年度</t>
@@ -2903,131 +3042,342 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>★14.86ポイントの差。掲載値22.07％は、修正前の累計額2,778,390,673円に当年度償却額393,745,802円を加えた3,172,136,475円を分子とすると22.02％となり、掲載値にほぼ一致する。過年度修正後の累計額が指標算定に反映されていない可能性が高い</t>
+          <t>★14.86ポイントの差。下表のとおり、分母の取り方を変えても掲載値には届かない。掲載値22.07％は分子（減価償却累計額）の側に過年度修正が反映されていないことによると考えられる</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>■　確認をお願いしたい事項と想定される影響</t>
+          <t>■　分子・分母の組合せによる検証（結論が分母の取り方に依存しないことの確認）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>分　子</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>分　母</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>比　率</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>掲載値22.07％との差</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>備　考</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>修正後の累計額（明細書・年度末）5,319,896,544</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>償却対象資産・年度末</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="n">
+        <v>36.93482838445267</v>
+      </c>
+      <c r="D20" s="28" t="n">
+        <v>14.86482838445267</v>
+      </c>
+      <c r="E20" s="15" t="inlineStr"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>修正後の累計額（明細書・年度末）5,319,896,544</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>償却対象資産・年度当初（修正前）</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="n">
+        <v>37.20013549014333</v>
+      </c>
+      <c r="D21" s="28" t="n">
+        <v>15.13013549014333</v>
+      </c>
+      <c r="E21" s="15" t="inlineStr"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>修正後の累計額（明細書・年度末）5,319,896,544</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>有形固定資産計・年度末（土地・建仮含む）</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="n">
+        <v>36.74015522686371</v>
+      </c>
+      <c r="D22" s="28" t="n">
+        <v>14.67015522686371</v>
+      </c>
+      <c r="E22" s="15" t="inlineStr"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>修正後の累計額（明細書・年度末）5,319,896,544</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>有形固定資産計・年度当初（土地・建仮含む）</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="n">
+        <v>37.07802686698586</v>
+      </c>
+      <c r="D23" s="28" t="n">
+        <v>15.00802686698586</v>
+      </c>
+      <c r="E23" s="15" t="inlineStr"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>修正前の累計額（R6末）2,778,390,673 ＋ 当年度償却393,745,802</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>償却対象資産・年度末</t>
+        </is>
+      </c>
+      <c r="C24" s="36" t="n">
+        <v>22.0234200697621</v>
+      </c>
+      <c r="D24" s="37" t="n">
+        <v>-0.04657993023789686</v>
+      </c>
+      <c r="E24" s="26" t="inlineStr"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>修正前の累計額（R6末）2,778,390,673 ＋ 当年度償却393,745,802</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>償却対象資産・年度当初（修正前）</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="n">
+        <v>22.18161682040892</v>
+      </c>
+      <c r="D25" s="37" t="n">
+        <v>0.1116168204089192</v>
+      </c>
+      <c r="E25" s="26" t="inlineStr"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>修正前の累計額（R6末）2,778,390,673 ＋ 当年度償却393,745,802</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>有形固定資産計・年度末（土地・建仮含む）</t>
+        </is>
+      </c>
+      <c r="C26" s="36" t="n">
+        <v>21.90734077784658</v>
+      </c>
+      <c r="D26" s="37" t="n">
+        <v>-0.1626592221534224</v>
+      </c>
+      <c r="E26" s="26" t="inlineStr"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>修正前の累計額（R6末）2,778,390,673 ＋ 当年度償却393,745,802</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>有形固定資産計・年度当初（土地・建仮含む）</t>
+        </is>
+      </c>
+      <c r="C27" s="36" t="n">
+        <v>22.1088061530912</v>
+      </c>
+      <c r="D27" s="37" t="n">
+        <v>0.03880615309120117</v>
+      </c>
+      <c r="E27" s="26" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>★ 修正後の累計額を分子とすると、分母をどう取っても36.7〜37.2％にしかなりません（上段４行）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>★ 一方、修正前の累計額に当年度償却額を加えた3,172,136,475円を分子とすると、分母をどう取っても21.9〜22.2％の範囲に収まり、掲載値22.07％を含みます（下段４行）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 したがって「分母の定義の違い」では説明がつかず、分子に過年度修正が反映されていないと考えるのが最も整合的です。ただし、これは外部からの推定であり、算定根拠の提示を受けたうえで確定させる必要があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>■　確認をお願いしたい事項と想定される影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>確認事項</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>想定される影響</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>対　応</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="56" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>決算書「経営指標の推移」の有形固定資産減価償却率22.07％の算定根拠（分子・分母の値）</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>町上下水道課・会計システム業者</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>決算状況調査（総務省）に同じ値を報告している場合、経営比較分析表の公表値にも同じ誤りが波及する</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>算定根拠の提示を求め、明細書の値と突合する</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr"/>
-    </row>
-    <row r="21" ht="56" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="E35" s="15" t="inlineStr"/>
+    </row>
+    <row r="36" ht="56" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>決算状況調査の該当項目に入力した値</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>町上下水道課</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>令和７年度の経営比較分析表（令和９年公表予定）に影響</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>提出済みの場合は訂正の要否を県と協議</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr"/>
-    </row>
-    <row r="22" ht="56" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr"/>
+    </row>
+    <row r="37" ht="56" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>会計システムの指標算定ロジックが過年度修正を取り込む仕様になっているか</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>会計システム業者</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>業務仕様書６(６)「会計システムの見直し」の検討材料となる。過年度修正を指標に反映できないシステムであれば、入替検討の論拠のひとつ</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>システム設定の確認を依頼。結果を(６)の報告に反映</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr"/>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>※ 本件は「決算書の数値が誤っている」という指摘ではありません。貸借対照表・損益計算書・固定資産明細書の各表は相互に整合しており、</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　 差異があるのは巻頭の「経営指標の推移」に掲載された比率のみです。指標の算定基礎を確認したうえで、必要に応じて訂正または注記を行う趣旨です。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="11">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3457,7 +3807,7 @@
           <t>Ａ案の年間増収が07で28,159千円、08で約35,000千円と不一致。Ｂ案の196,136千円は改定後収入額</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>★Ａ案：約37,070千円（調定データ再計算）
 ★Ｂ案：39,392千円（04シートB15の必要増収額）</t>
@@ -3583,7 +3933,7 @@
           <t>R8〜R12</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>★R9〜R13</t>
         </is>
@@ -3610,7 +3960,7 @@
           <t>1,042,625千円</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>★2,396,601千円（R8末）</t>
         </is>
@@ -3637,7 +3987,7 @@
           <t>750,000千円</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>★3,838,050千円（R13末）</t>
         </is>
@@ -3664,7 +4014,7 @@
           <t>自動計算</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>★3,117,326千円</t>
         </is>
@@ -3691,7 +4041,7 @@
           <t>4,316,000㎥</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>★4,690,698㎥</t>
         </is>
@@ -3718,7 +4068,7 @@
           <t>5年計 ▲450,000千円</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>★▲1,510,688千円</t>
         </is>
@@ -3745,7 +4095,7 @@
           <t>52.87％（R5の値）</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>★35.07％（R7）</t>
         </is>
@@ -3772,7 +4122,7 @@
           <t>約242円（R5実績逆算）</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>★332.50円（R7・経営比較分析表の算式）</t>
         </is>
@@ -3801,7 +4151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4011,7 +4361,7 @@
           <t>現行</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <v>10069576</v>
       </c>
       <c r="C12" s="33" t="n"/>
@@ -4032,19 +4382,20 @@
     <row r="13" ht="66" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>★案3-A（口径別・標準逓増）</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="n">
+          <t>★案3-A（口径別・標準逓増）
+【前提】メーター使用料は基本料金に統合</t>
+        </is>
+      </c>
+      <c r="B13" s="38" t="n">
         <v>11232023</v>
       </c>
-      <c r="C13" s="36" t="n">
+      <c r="C13" s="38" t="n">
         <v>1162447</v>
       </c>
       <c r="D13" s="27" t="n">
         <v>11.54415041904446</v>
       </c>
-      <c r="E13" s="36" t="n">
+      <c r="E13" s="38" t="n">
         <v>13793037.50180247</v>
       </c>
       <c r="F13" s="13" t="inlineStr">
@@ -4060,502 +4411,541 @@
       </c>
     </row>
     <row r="14" ht="66" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>【感応度】案3-A
+ メーター使用料を別建てで据置く場合</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>11493163</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>1423587</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>14.13750688211699</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>16891599.254055</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>税抜133.10円
+税込146.41円</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>★05シートの試算列にメーター使用料が含まれていないため、統合か据置かが判別できない。据置く設計なら増収率は＋14.14％、年間増収は16,892千円となる。【要確認事項】どちらの設計かを確定させる必要がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>★基本1.5倍＋超過+22円</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n">
+      <c r="B15" s="38" t="n">
         <v>13158717</v>
       </c>
-      <c r="C14" s="36" t="n">
+      <c r="C15" s="38" t="n">
         <v>3089141</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D15" s="27" t="n">
         <v>30.67796499078015</v>
       </c>
-      <c r="E14" s="36" t="n">
+      <c r="E15" s="38" t="n">
         <v>36654262.65572155</v>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>税抜152.39円
 税込167.63円</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>★02シートB24の「約192円」は誤り。192円は現行供給単価128.2円（税込）を単純に1.5倍した値</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>■　水量帯別の影響（案3-A）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>■　水量帯別の影響（案3-A・メーター使用料は基本料金に統合する前提）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>水量帯</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>水量（㎥）</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>現行（円）</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>案3-A（円）</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>増減率</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>コメント</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>① 0㎥</t>
-        </is>
-      </c>
-      <c r="B18" s="36" t="n">
-        <v>314</v>
-      </c>
-      <c r="C18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="36" t="n">
-        <v>331133</v>
-      </c>
-      <c r="E18" s="36" t="n">
-        <v>400180</v>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>20.85174235126068</v>
-      </c>
-      <c r="G18" s="15" t="inlineStr"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
+          <t>① 0㎥</t>
+        </is>
+      </c>
+      <c r="B19" s="38" t="n">
+        <v>314</v>
+      </c>
+      <c r="C19" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="38" t="n">
+        <v>331133</v>
+      </c>
+      <c r="E19" s="38" t="n">
+        <v>400180</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>20.85174235126068</v>
+      </c>
+      <c r="G19" s="15" t="inlineStr"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
           <t>② 1〜5㎥</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n">
+      <c r="B20" s="38" t="n">
         <v>561</v>
       </c>
-      <c r="C19" s="36" t="n">
+      <c r="C20" s="38" t="n">
         <v>1667</v>
       </c>
-      <c r="D19" s="36" t="n">
+      <c r="D20" s="38" t="n">
         <v>593956</v>
       </c>
-      <c r="E19" s="36" t="n">
+      <c r="E20" s="38" t="n">
         <v>732160</v>
       </c>
-      <c r="F19" s="27" t="n">
+      <c r="F20" s="27" t="n">
         <v>23.26839025112972</v>
       </c>
-      <c r="G19" s="15" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="G20" s="15" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>③ 6〜10㎥</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B21" s="18" t="n">
         <v>625</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C21" s="18" t="n">
         <v>4994</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <v>802637</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E21" s="18" t="n">
         <v>806520</v>
       </c>
-      <c r="F20" s="31" t="n">
+      <c r="F21" s="31" t="n">
         <v>0.4837803390573825</v>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>④ 11〜20㎥</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B22" s="19" t="n">
         <v>859</v>
       </c>
-      <c r="C21" s="18" t="n">
+      <c r="C22" s="19" t="n">
         <v>12949</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D22" s="19" t="n">
         <v>1630849</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E22" s="19" t="n">
         <v>1687488</v>
       </c>
-      <c r="F21" s="32" t="n">
+      <c r="F22" s="32" t="n">
         <v>3.472976345449519</v>
       </c>
-      <c r="G21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>⑤ 21〜50㎥</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B23" s="18" t="n">
         <v>579</v>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C23" s="18" t="n">
         <v>16356</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D23" s="18" t="n">
         <v>2025221</v>
       </c>
-      <c r="E22" s="17" t="n">
+      <c r="E23" s="18" t="n">
         <v>2186415</v>
       </c>
-      <c r="F22" s="31" t="n">
+      <c r="F23" s="31" t="n">
         <v>7.959328883119432</v>
       </c>
-      <c r="G22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>⑥ 51〜100㎥</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="n">
-        <v>47</v>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>3266</v>
-      </c>
-      <c r="D23" s="22" t="n">
-        <v>403205</v>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>490688</v>
-      </c>
-      <c r="F23" s="29" t="n">
-        <v>21.69690356022371</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
+          <t>⑥ 51〜100㎥</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>47</v>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>3266</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>403205</v>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>490688</v>
+      </c>
+      <c r="F24" s="29" t="n">
+        <v>21.69690356022371</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
           <t>⑦ 101〜500㎥</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B25" s="22" t="n">
         <v>51</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C25" s="22" t="n">
         <v>10248</v>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D25" s="22" t="n">
         <v>1201145</v>
       </c>
-      <c r="E24" s="22" t="n">
+      <c r="E25" s="22" t="n">
         <v>1446698</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F25" s="29" t="n">
         <v>20.4432437382664</v>
       </c>
-      <c r="G24" s="12" t="inlineStr"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>⑧ 501㎥超</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B26" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C25" s="18" t="n">
+      <c r="C26" s="19" t="n">
         <v>27694</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D26" s="19" t="n">
         <v>3081430</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E26" s="19" t="n">
         <v>3481874</v>
       </c>
-      <c r="F25" s="32" t="n">
+      <c r="F26" s="32" t="n">
         <v>12.99539499518081</v>
       </c>
-      <c r="G25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>★合計</t>
         </is>
       </c>
-      <c r="B26" s="24" t="n">
+      <c r="B27" s="24" t="n">
         <v>3056</v>
       </c>
-      <c r="C26" s="24" t="n">
+      <c r="C27" s="24" t="n">
         <v>77174</v>
       </c>
-      <c r="D26" s="24" t="n">
+      <c r="D27" s="24" t="n">
         <v>10069576</v>
       </c>
-      <c r="E26" s="24" t="n">
+      <c r="E27" s="24" t="n">
         <v>11232023</v>
       </c>
-      <c r="F26" s="37" t="n">
+      <c r="F27" s="36" t="n">
         <v>11.54415041904446</v>
       </c>
-      <c r="G26" s="26" t="inlineStr"/>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="G27" s="26" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>★ 案3-Aは、口径別基本料金の導入により 0㎥・少量利用者（875件・全体の29％）の負担が＋21〜23％と最も大きくなります。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="21" t="inlineStr">
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　 一方、11〜20㎥の標準的な世帯は＋3.5％にとどまり、13mmの標準世帯（20㎥）はメーター使用料が基本料金に統合されるため実質△2.2％となります。</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　 「大口の負担が増える体系」という説明は成立しません。逆進的な負担配分となる点を、住民説明の前に整理しておく必要があります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 「大口の負担が増える体系」という説明は成立しません。少量利用者に負担が偏る配分となる点を、住民説明の前に整理しておく必要があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>※ ただし0㎥の314件には休止中の給水装置・空き家が含まれる可能性があり、そのすべてが生活困窮世帯というわけではありません。用途区分・休止区分との突合が必要です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>■　モデルケース別の影響</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>区　分</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>現行（円）</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>案3-A（円）</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>増減率</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>基本1.5倍＋22円（円）</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>増減率</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>備　考</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>小規模（家族経営）
 25mm・200㎥／月（5社）</t>
         </is>
       </c>
-      <c r="B34" s="17" t="n">
+      <c r="B36" s="18" t="n">
         <v>23210</v>
       </c>
-      <c r="C34" s="17" t="n">
+      <c r="C36" s="18" t="n">
         <v>26510</v>
       </c>
-      <c r="D34" s="31" t="n">
+      <c r="D36" s="31" t="n">
         <v>14.21800947867298</v>
       </c>
-      <c r="E34" s="17" t="n">
+      <c r="E36" s="18" t="n">
         <v>27940</v>
       </c>
-      <c r="F34" s="31" t="n">
+      <c r="F36" s="31" t="n">
         <v>20.37914691943128</v>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>中規模（一般加工）
 50mm・1,000㎥／月（8社）</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B37" s="19" t="n">
         <v>111980</v>
       </c>
-      <c r="C35" s="18" t="n">
+      <c r="C37" s="19" t="n">
         <v>127050</v>
       </c>
-      <c r="D35" s="32" t="n">
+      <c r="D37" s="32" t="n">
         <v>13.45776031434185</v>
       </c>
-      <c r="E35" s="18" t="n">
+      <c r="E37" s="19" t="n">
         <v>134310</v>
       </c>
-      <c r="F35" s="32" t="n">
+      <c r="F37" s="32" t="n">
         <v>19.9410609037328</v>
       </c>
-      <c r="G35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>大規模（冷凍・主要）
 75mm・3,000㎥／月（5社）</t>
         </is>
       </c>
-      <c r="B36" s="17" t="n">
+      <c r="B38" s="18" t="n">
         <v>332200</v>
       </c>
-      <c r="C36" s="17" t="n">
+      <c r="C38" s="18" t="n">
         <v>373450</v>
       </c>
-      <c r="D36" s="31" t="n">
+      <c r="D38" s="31" t="n">
         <v>12.41721854304636</v>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E38" s="18" t="n">
         <v>398530</v>
       </c>
-      <c r="F36" s="31" t="n">
+      <c r="F38" s="31" t="n">
         <v>19.96688741721855</v>
       </c>
-      <c r="G36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>超大口（大手）
 100mm・8,000㎥／月（1社）</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B39" s="19" t="n">
         <v>882420</v>
       </c>
-      <c r="C37" s="18" t="n">
+      <c r="C39" s="19" t="n">
         <v>985050</v>
       </c>
-      <c r="D37" s="32" t="n">
+      <c r="D39" s="32" t="n">
         <v>11.63051608077785</v>
       </c>
-      <c r="E37" s="18" t="n">
+      <c r="E39" s="19" t="n">
         <v>1058750</v>
       </c>
-      <c r="F37" s="32" t="n">
+      <c r="F39" s="32" t="n">
         <v>19.9825479930192</v>
       </c>
-      <c r="G37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>標準世帯
 13mm・20㎥／月</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n">
+      <c r="B40" s="22" t="n">
         <v>2475</v>
       </c>
-      <c r="C38" s="22" t="n">
+      <c r="C40" s="22" t="n">
         <v>2420</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D40" s="29" t="n">
         <v>-2.222222222222225</v>
       </c>
-      <c r="E38" s="22" t="n">
+      <c r="E40" s="22" t="n">
         <v>3245</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F40" s="29" t="n">
         <v>31.11111111111111</v>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>★08シートの「現行2,395円」は根拠不明。正しくは2,475円（税込）</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="21" t="inlineStr">
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>※ 06シートのG列（現行体系＋22円超過）・H列（基本1.5倍＋22円）の試算表の値は、当方の再計算と一致しています。誤っているのはA13の本文コメントのみです。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="21" t="inlineStr">
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>※ 水産加工業19社の月間使用水量は推計値です。実使用水量データの提供をお願いします。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A34:G34"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4793,7 +5183,7 @@
           <t>－</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>★08シートの2,395円は根拠不明。調定データの13mm・20㎥の実績額と一致するのは2,475円</t>
         </is>
@@ -4810,7 +5200,7 @@
           <t>基本1,320〜1,540円＋従量132〜143円／㎥＋メーター55円</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>2,695〜3,025</t>
         </is>
@@ -4866,7 +5256,7 @@
           <t>13mm基本1,100円（10㎥込み）＋従量132円／㎥（メーター使用料は基本料金に統合）</t>
         </is>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="39" t="inlineStr">
         <is>
           <t>2,420</t>
         </is>
@@ -4991,14 +5381,14 @@
       <c r="E23" s="12" t="inlineStr"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>※ 資産維持率は1.0％／1.5％／2.0％／2.5％／3.0％で試算済みです（詳細は「女川町_水道_数値定義と確定値一覧.xlsx」）。最終決定をお願いします。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>※ 対象資産は料金算定対象期間（令和９〜13年度）の期首期末平均3,117,326千円としています（水道料金算定要領）。</t>
         </is>
@@ -5016,4 +5406,712 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>８　本分析の前提・限界と要確認事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>本ファイルの数値を住民・議会説明に用いる前に確認すべき事項。推定を含む箇所を明示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>■　確定値と推計値の区別</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>項　目</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>根　拠</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>確からしさ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>過年度修正の修正前・修正後の額（上水道11項目・下水道３項目）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>決算審査意見書「参考 過年度審査指摘事項」の記載どおり</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>★意見書は「案・初稿」。確定版で額が変わりうるため、最終報告時に再突合が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>令和６年度末の資本金・資本剰余金・未処理欠損金</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>令和７年度剰余金計算書の「前年度末残高」</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>決算書の記載どおり。検証不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>令和６年度末の償却資産の帳簿原価・減価償却累計額</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>令和７年度有形固定資産明細書の「年度当初の現在高」＋意見書の修正額</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>修正前の累計額から算定した償却率19.43％が決算書掲載値と一致することで裏づけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>過年度修正の純影響額 1,558,605,676円</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>貸借対照表等式による算定</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>令和７年度の特別損益（当年度分を除く）と差異０円で一致。二重に検証済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>★推計</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>令和６年度末の流動資産 417,612千円</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>令和７年度の流動資産156,291千円＋意見書の前年度比減少額261,321千円</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>★意見書の記載が千円単位のため、円単位の精度はない。この値から算定した自己資本構成比率が決算書掲載値90.07％を再現することで妥当性を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>★推計</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>令和６年度末の流動負債 218,851千円</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>上記の流動資産を決算書掲載の流動比率190.82％で除して逆算</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>★流動資産の推計値と掲載比率（小数第２位）に依存。修正後の流動比率111.52％も同じ誤差を引き継ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>★推計</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>令和６年度の営業収益 118,811千円（累積欠損金比率の分母）</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>給水収益118,769千円（意見書の前年度比増加額から逆算）＋その他営業収益41千円（令和７年度の額を流用）</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>★令和６年度のその他営業収益は未確認。累積欠損金比率の値は±数ポイントの幅がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>★推定</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>令和７年度掲載値22.07％の算定根拠</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>分子・分母の８通りの組合せによる検証</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>★分子に過年度修正が反映されていないと考えるのが最も整合的だが、外部からの推定。算定根拠の提示を受けて確定させる必要がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>■　料金改定試算の前提と限界</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>前提・限界</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>影　響</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>対　応</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>★案3-Aでメーター使用料を廃止（基本料金に統合）するか、別建てで据え置くかが05シートから判別できない</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>統合なら増収率＋11.54％（年間13,793千円）、据置なら＋14.14％（年間16,892千円）。約3,100千円の差</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>★設計意図の確認をお願いします。本ファイルは「統合」を前提として算定しています</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>★調定データは令和７年度の１か月分。有収水量77,174㎥は年間実績の月平均85,381㎥を9.6％下回る</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>★水産加工業などの大口は増収率が低い（＋11.6〜13.5％）ため、大口の使用が多い月を含めた年間ベースでは増収率が11.54％を下回る可能性がある</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>12か月分の調定データがあれば精緻化できます。中間報告では「推計値」と明記して使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>年間増収額は「増収率×令和７年度給水収益」で算定している</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>月次実額×12で算定すると13,949千円となり、156千円の差が生じる</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>決算確定値に接続する前者を採用。両方を併記しています</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>水産加工業19社の月間使用水量は推計値（06シートの値をそのまま使用）</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>モデルケース別の増減率（＋11.6〜14.2％）は実態と乖離する可能性がある</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>実使用水量データの提供をお願いします</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>必要改定率（＋184.4〜241.4％、キャッシュ不足額ベース＋39.7〜66.5％）は既報の算定値</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>本ファイルでは再検証していない</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>「女川町_水道_数値定義と確定値一覧.xlsx」を参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>■　本ファイルで対応できていない範囲</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>項　目</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>理　由</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>必要な資料・作業</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>下水道事業の指標対比（有収率・経常収支比率・処理原価・使用料単価等）</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>令和６年度の下水道事業貸借対照表・損益計算書の明細を突合できていない</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>令和６年度下水道事業会計決算書。未処理欠損金の対比のみ本ファイル シート02末尾に掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>浄化槽事業（特定地域生活排水処理事業）の指標対比</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>企業会計移行前のため、修正前後の対比という枠組みが適用できない</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>企業会計移行後の開始貸借対照表。仕様書６(４)の作業と一体で実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>決算状況調査に報告した値との突合</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>提出済みの調査票を入手できていない</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>令和７年度決算状況調査の提出データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>■　確認・決定をお願いしたい事項（既報分を含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>事　項</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>なぜ必要か</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>状　況</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>「3パターン」「資産維持費3％」の根拠</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>いただいた仕様書に記載がありません</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>既報・未回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>経営戦略の「様式を変更しない形で」の解釈</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>経営目標の数値化・ロードマップ追加の可否で成果物が変わります</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>既報・未回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>中間報告の主軸を定義③（キャッシュ不足額）とすることの可否</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>総括原価ベースを前面に出すと、提示できる改定案がすべて充足率10％未満となり報告が成立しません</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>既報・未回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>資産維持率の最終決定（1.0／1.5／2.0／2.5／3.0％）</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>赤字半減の改定率が＋39.7％／＋53.1％／＋66.5％と変わります</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>既報・未回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>水産加工業19社の実使用水量</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>06シートは推計値のままです</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>既報・未提供</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>例月出納検査・予算書案作成の実施体制</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>工程表への反映が必要です</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>既報・未回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="35" t="inlineStr">
+        <is>
+          <t>★7</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>決算書掲載の有形固定資産減価償却率22.07％の算定根拠</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>決算状況調査・経営比較分析表に波及するため</t>
+        </is>
+      </c>
+      <c r="D37" s="35" t="inlineStr">
+        <is>
+          <t>★本書で新たに提起</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>★8</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>決算状況調査に報告した有形固定資産減価償却率の値</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>訂正の要否を県と協議する必要が生じる可能性があります</t>
+        </is>
+      </c>
+      <c r="D38" s="35" t="inlineStr">
+        <is>
+          <t>★本書で新たに提起</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>★9</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>案3-Aにおけるメーター使用料の取扱い（統合／別建て据置）</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>年間増収額が約3,100千円変わります</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="inlineStr">
+        <is>
+          <t>★本書で新たに提起</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>